--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCategory/2026/202608/Category_P&L_20260803.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCategory/2026/202608/Category_P&L_20260803.xlsx
@@ -44917,7 +44917,7 @@
         <v>46233</v>
       </c>
       <c r="B1172">
-        <v>85859219.67</v>
+        <v>87859219.67</v>
       </c>
       <c r="C1172">
         <v>2560679.54</v>
@@ -44955,19 +44955,19 @@
         <v>46234</v>
       </c>
       <c r="B1173">
-        <v>86263492.97</v>
+        <v>88263665.98999999</v>
       </c>
       <c r="C1173">
         <v>409896.17</v>
       </c>
       <c r="D1173">
-        <v>0.004774</v>
+        <v>0.004665</v>
       </c>
       <c r="E1173">
         <v>9174.1</v>
       </c>
       <c r="F1173">
-        <v>0.000107</v>
+        <v>0.000104</v>
       </c>
       <c r="G1173">
         <v>-2</v>
@@ -44993,19 +44993,19 @@
         <v>46237</v>
       </c>
       <c r="B1174">
-        <v>87113767.19</v>
+        <v>89113874.08</v>
       </c>
       <c r="C1174">
-        <v>943725.96</v>
+        <v>943140.77</v>
       </c>
       <c r="D1174">
-        <v>0.01094</v>
+        <v>0.010685</v>
       </c>
       <c r="E1174">
         <v>-133023.1</v>
       </c>
       <c r="F1174">
-        <v>-0.001542</v>
+        <v>-0.001507</v>
       </c>
       <c r="G1174">
         <v>112</v>
